--- a/r4-core-157-add-vbpk-as-patientidentifier/StructureDefinition-at-core-practitioner.xlsx
+++ b/r4-core-157-add-vbpk-as-patientidentifier/StructureDefinition-at-core-practitioner.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2848" uniqueCount="419">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2851" uniqueCount="422">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T10:22:16+00:00</t>
+    <t>2026-10-07T08:52:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -722,6 +722,12 @@
   </si>
   <si>
     <t>Practitioner.identifier:GDA-OID.type</t>
+  </si>
+  <si>
+    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
   </si>
   <si>
     <t>Practitioner.identifier:GDA-OID.system</t>
@@ -1052,6 +1058,10 @@
   </si>
   <si>
     <t>The home/mailing address of the practitioner is often required for employee administration purposes, and also for some rostering services where the start point (practitioners home) can be used in calculations.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+at-addr-1:If the extension for street name is used then the value for line must not be empty {line.all($this.extension('http://hl7.org/fhir/StructureDefinition/iso21090-ADXP-streetName').empty() or $this.hasValue())}at-addr-2:If the extension for street number is used then the value for line must not be empty {line.all($this.extension('http://hl7.org/fhir/StructureDefinition/iso21090-ADXP-houseNumber').empty() or $this.hasValue())}at-addr-3:If the extension for floor/door number is used then the value for line must not be empty {line.all($this.extension('http://hl7.org/fhir/StructureDefinition/iso21090-ADXP-additionalLocator').empty() or $this.hasValue())}</t>
   </si>
   <si>
     <t>ORC-24, STF-11, ROL-11, PRT-14</t>
@@ -1654,7 +1664,7 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="51.97265625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="84.33984375" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="46.58203125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
@@ -4366,9 +4376,11 @@
       <c r="X24" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="Y24" s="2"/>
+      <c r="Y24" t="s" s="2">
+        <v>229</v>
+      </c>
       <c r="Z24" t="s" s="2">
-        <v>184</v>
+        <v>230</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>21</v>
@@ -4415,7 +4427,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B25" t="s" s="2">
         <v>187</v>
@@ -4444,7 +4456,7 @@
         <v>102</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="M25" t="s" s="2">
         <v>189</v>
@@ -4460,7 +4472,7 @@
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="S25" t="s" s="2">
         <v>21</v>
@@ -4531,7 +4543,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B26" t="s" s="2">
         <v>197</v>
@@ -4560,7 +4572,7 @@
         <v>157</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="M26" t="s" s="2">
         <v>199</v>
@@ -4645,7 +4657,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B27" t="s" s="2">
         <v>206</v>
@@ -4757,7 +4769,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B28" t="s" s="2">
         <v>214</v>
@@ -4871,10 +4883,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4983,10 +4995,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5097,10 +5109,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5126,13 +5138,13 @@
         <v>157</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5182,7 +5194,7 @@
         <v>21</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5191,7 +5203,7 @@
         <v>88</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>100</v>
@@ -5211,10 +5223,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5240,13 +5252,13 @@
         <v>102</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5275,10 +5287,10 @@
         <v>183</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>21</v>
@@ -5296,7 +5308,7 @@
         <v>21</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5325,10 +5337,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5354,13 +5366,13 @@
         <v>146</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5410,7 +5422,7 @@
         <v>21</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5428,7 +5440,7 @@
         <v>21</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>21</v>
@@ -5439,10 +5451,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5468,13 +5480,13 @@
         <v>157</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5482,7 +5494,7 @@
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>21</v>
@@ -5524,7 +5536,7 @@
         <v>21</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5553,13 +5565,13 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B35" t="s" s="2">
         <v>145</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D35" t="s" s="2">
         <v>21</v>
@@ -5669,7 +5681,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B36" t="s" s="2">
         <v>156</v>
@@ -5781,7 +5793,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B37" t="s" s="2">
         <v>162</v>
@@ -5895,7 +5907,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B38" t="s" s="2">
         <v>167</v>
@@ -6011,7 +6023,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B39" t="s" s="2">
         <v>177</v>
@@ -6076,9 +6088,11 @@
       <c r="X39" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="Y39" s="2"/>
+      <c r="Y39" t="s" s="2">
+        <v>229</v>
+      </c>
       <c r="Z39" t="s" s="2">
-        <v>184</v>
+        <v>230</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>21</v>
@@ -6125,7 +6139,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B40" t="s" s="2">
         <v>187</v>
@@ -6154,7 +6168,7 @@
         <v>102</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="M40" t="s" s="2">
         <v>189</v>
@@ -6170,7 +6184,7 @@
       </c>
       <c r="Q40" s="2"/>
       <c r="R40" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="S40" t="s" s="2">
         <v>21</v>
@@ -6241,7 +6255,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B41" t="s" s="2">
         <v>197</v>
@@ -6355,7 +6369,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B42" t="s" s="2">
         <v>206</v>
@@ -6467,7 +6481,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B43" t="s" s="2">
         <v>214</v>
@@ -6581,10 +6595,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6693,10 +6707,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6807,10 +6821,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6836,13 +6850,13 @@
         <v>157</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6892,7 +6906,7 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -6901,7 +6915,7 @@
         <v>88</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>100</v>
@@ -6921,10 +6935,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6950,13 +6964,13 @@
         <v>102</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -6985,10 +6999,10 @@
         <v>183</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>21</v>
@@ -7006,7 +7020,7 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7035,10 +7049,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7064,13 +7078,13 @@
         <v>146</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7120,7 +7134,7 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7138,7 +7152,7 @@
         <v>21</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>21</v>
@@ -7149,10 +7163,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7178,13 +7192,13 @@
         <v>157</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7192,7 +7206,7 @@
       </c>
       <c r="Q49" s="2"/>
       <c r="R49" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="S49" t="s" s="2">
         <v>21</v>
@@ -7234,7 +7248,7 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7263,13 +7277,13 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B50" t="s" s="2">
         <v>145</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="D50" t="s" s="2">
         <v>21</v>
@@ -7379,7 +7393,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B51" t="s" s="2">
         <v>156</v>
@@ -7491,7 +7505,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B52" t="s" s="2">
         <v>162</v>
@@ -7605,7 +7619,7 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B53" t="s" s="2">
         <v>167</v>
@@ -7721,7 +7735,7 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B54" t="s" s="2">
         <v>177</v>
@@ -7786,9 +7800,11 @@
       <c r="X54" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="Y54" s="2"/>
+      <c r="Y54" t="s" s="2">
+        <v>229</v>
+      </c>
       <c r="Z54" t="s" s="2">
-        <v>184</v>
+        <v>230</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>21</v>
@@ -7835,7 +7851,7 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B55" t="s" s="2">
         <v>187</v>
@@ -7864,7 +7880,7 @@
         <v>102</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="M55" t="s" s="2">
         <v>189</v>
@@ -7902,7 +7918,7 @@
       </c>
       <c r="Y55" s="2"/>
       <c r="Z55" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>21</v>
@@ -7949,7 +7965,7 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B56" t="s" s="2">
         <v>197</v>
@@ -8063,7 +8079,7 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B57" t="s" s="2">
         <v>206</v>
@@ -8175,7 +8191,7 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B58" t="s" s="2">
         <v>214</v>
@@ -8289,10 +8305,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8315,70 +8331,70 @@
         <v>89</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="P59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q59" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="R59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF59" t="s" s="2">
         <v>302</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="P59" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q59" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="R59" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S59" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T59" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U59" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V59" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W59" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X59" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y59" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z59" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA59" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB59" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC59" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD59" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE59" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF59" t="s" s="2">
-        <v>300</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -8396,21 +8412,21 @@
         <v>21</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8433,19 +8449,19 @@
         <v>89</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>21</v>
@@ -8494,7 +8510,7 @@
         <v>21</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -8509,13 +8525,13 @@
         <v>100</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>21</v>
@@ -8523,10 +8539,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8549,19 +8565,19 @@
         <v>89</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>21</v>
@@ -8610,7 +8626,7 @@
         <v>21</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -8625,13 +8641,13 @@
         <v>100</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>21</v>
@@ -8639,10 +8655,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8665,19 +8681,19 @@
         <v>89</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>21</v>
@@ -8726,7 +8742,7 @@
         <v>21</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -8738,16 +8754,16 @@
         <v>21</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>100</v>
+        <v>335</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>21</v>
@@ -8755,10 +8771,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8784,14 +8800,14 @@
         <v>108</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>21</v>
@@ -8819,10 +8835,10 @@
         <v>172</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>21</v>
@@ -8840,7 +8856,7 @@
         <v>21</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -8855,13 +8871,13 @@
         <v>100</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>21</v>
@@ -8869,10 +8885,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8898,10 +8914,10 @@
         <v>157</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -8981,10 +8997,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9010,10 +9026,10 @@
         <v>134</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9091,13 +9107,13 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="B66" t="s" s="2">
         <v>351</v>
       </c>
-      <c r="B66" t="s" s="2">
-        <v>348</v>
-      </c>
       <c r="C66" t="s" s="2">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="D66" t="s" s="2">
         <v>21</v>
@@ -9119,13 +9135,13 @@
         <v>21</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9185,7 +9201,7 @@
         <v>79</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="AJ66" t="s" s="2">
         <v>139</v>
@@ -9205,10 +9221,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9234,10 +9250,10 @@
         <v>157</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9288,7 +9304,7 @@
         <v>21</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -9317,10 +9333,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9343,17 +9359,17 @@
         <v>89</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>21</v>
@@ -9402,7 +9418,7 @@
         <v>21</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -9417,13 +9433,13 @@
         <v>100</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>21</v>
@@ -9431,10 +9447,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9457,17 +9473,17 @@
         <v>21</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" t="s" s="2">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>21</v>
@@ -9516,7 +9532,7 @@
         <v>21</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -9534,10 +9550,10 @@
         <v>21</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>21</v>
@@ -9545,10 +9561,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9571,13 +9587,13 @@
         <v>21</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -9628,7 +9644,7 @@
         <v>21</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -9643,13 +9659,13 @@
         <v>100</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>21</v>
@@ -9657,10 +9673,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9769,10 +9785,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9883,14 +9899,14 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
@@ -9912,10 +9928,10 @@
         <v>134</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="N73" t="s" s="2">
         <v>137</v>
@@ -9970,7 +9986,7 @@
         <v>21</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -9999,10 +10015,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10028,14 +10044,14 @@
         <v>146</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" t="s" s="2">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>21</v>
@@ -10084,7 +10100,7 @@
         <v>21</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -10102,7 +10118,7 @@
         <v>21</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>21</v>
@@ -10113,10 +10129,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10142,10 +10158,10 @@
         <v>178</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -10172,31 +10188,31 @@
         <v>21</v>
       </c>
       <c r="X75" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="Y75" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="Z75" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="AA75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF75" t="s" s="2">
         <v>397</v>
-      </c>
-      <c r="Y75" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="Z75" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="AA75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF75" t="s" s="2">
-        <v>394</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>88</v>
@@ -10214,10 +10230,10 @@
         <v>21</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>21</v>
@@ -10225,10 +10241,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10254,14 +10270,14 @@
         <v>207</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" t="s" s="2">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>21</v>
@@ -10310,7 +10326,7 @@
         <v>21</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
@@ -10328,10 +10344,10 @@
         <v>21</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>21</v>
@@ -10339,10 +10355,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10368,10 +10384,10 @@
         <v>215</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -10422,7 +10438,7 @@
         <v>21</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
@@ -10440,7 +10456,7 @@
         <v>21</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>21</v>
@@ -10451,10 +10467,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10480,16 +10496,16 @@
         <v>178</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>21</v>
@@ -10538,7 +10554,7 @@
         <v>21</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -10553,13 +10569,13 @@
         <v>100</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>21</v>
